--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>334.38</v>
+        <v>334.22</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>317.87</v>
+        <v>318.35</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>284.55</v>
+        <v>284.83</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>71.69</v>
+        <v>71.12</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=71.7); volume elevated on pullback (ratio=1.16)</t>
+          <t>RSI not pulled back (RSI=71.1); volume elevated on pullback (ratio=1.16)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>495.17</v>
+        <v>507.62</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>453.11</v>
+        <v>455.47</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>429.65</v>
+        <v>429.84</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>57.25</v>
+        <v>61.2</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=57.2)</t>
+          <t>RSI not pulled back (RSI=61.2)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>340.54</v>
+        <v>348.94</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>347.02</v>
+        <v>346.76</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>336.39</v>
+        <v>336.54</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46.45</v>
+        <v>50.89</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,17 +616,17 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K4" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=46.4); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-3.39)</t>
+          <t>RSI not pulled back (RSI=50.9); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.44)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>255.74</v>
+        <v>255.23</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>255.23</v>
+        <v>255.5</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>239.79</v>
+        <v>239.94</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46.84</v>
+        <v>42.39</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=46.8); MACD below zero line (momentum turned negative, MACD=-0.92)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-0.92)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>219.15</v>
+        <v>212.29</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>212.37</v>
+        <v>212.71</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>197.11</v>
+        <v>197.26</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>53.12</v>
+        <v>52.73</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>4.8</v>
+        <v>7.7</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=53.1)</t>
+          <t>RSI not pulled back (RSI=52.7)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>648.27</v>
+        <v>665.29</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>600.91</v>
+        <v>602.55</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>622.58</v>
+        <v>622.85</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>83.92</v>
+        <v>84.75</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=83.9); volume elevated on pullback (ratio=1.15)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=84.7); volume elevated on pullback (ratio=1.17)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>365.42</v>
+        <v>361.01</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>354.5</v>
+        <v>353.85</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>398.93</v>
+        <v>398.64</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>50.99</v>
+        <v>55.05</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>14.1</v>
+        <v>15.1</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=51.0); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=55.1); SMA50 flattening/falling (trend weakening); pullback too deep (15.1% off high)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>334.22</v>
+        <v>329.88</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>318.35</v>
+        <v>318.67</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>284.83</v>
+        <v>285.09</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>71.12</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=71.1); volume elevated on pullback (ratio=1.16)</t>
+          <t>RSI not pulled back (RSI=67.2); volume elevated on pullback (ratio=1.15)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>507.62</v>
+        <v>499.56</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>455.47</v>
+        <v>457.7</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>429.84</v>
+        <v>429.95</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>61.2</v>
+        <v>54.37</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=61.2)</t>
+          <t>RSI not pulled back (RSI=54.4)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>348.94</v>
+        <v>343.05</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>346.76</v>
+        <v>346.31</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>336.54</v>
+        <v>336.64</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>50.89</v>
+        <v>47.29</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=50.9); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.44)</t>
+          <t>RSI not pulled back (RSI=47.3); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-1.99)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>255.23</v>
+        <v>248.56</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>255.5</v>
+        <v>255.56</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>239.94</v>
+        <v>240.03</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>42.39</v>
+        <v>37.64</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>10.1</v>
+        <v>12.5</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-0.92)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-1.61)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>212.29</v>
+        <v>211.28</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>212.71</v>
+        <v>213</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>197.26</v>
+        <v>197.42</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>52.73</v>
+        <v>48.92</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=52.7)</t>
+          <t>RSI not pulled back (RSI=48.9)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>665.29</v>
+        <v>666.03</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>602.55</v>
+        <v>603.87</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>622.85</v>
+        <v>623.01</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>84.75</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=84.7); volume elevated on pullback (ratio=1.17)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=83.6); volume elevated on pullback (ratio=1.15)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>361.01</v>
+        <v>358.97</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>353.85</v>
+        <v>352.59</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>398.64</v>
+        <v>398.33</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>55.05</v>
+        <v>53.63</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=55.1); SMA50 flattening/falling (trend weakening); pullback too deep (15.1% off high)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=53.6); SMA50 flattening/falling (trend weakening); pullback too deep (15.6% off high)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,25 +510,25 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>329.88</v>
+        <v>333.13</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>318.67</v>
+        <v>319.16</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>285.09</v>
+        <v>285.38</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>67.18000000000001</v>
+        <v>67.91</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H2" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=67.2); volume elevated on pullback (ratio=1.15)</t>
+          <t>RSI not pulled back (RSI=67.9)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>499.56</v>
+        <v>493.77</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>457.7</v>
+        <v>459.76</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>429.95</v>
+        <v>430</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>54.37</v>
+        <v>48.57</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=54.4)</t>
+          <t>RSI not pulled back (RSI=48.6)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>343.05</v>
+        <v>345.19</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>346.31</v>
+        <v>345.91</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>336.64</v>
+        <v>336.78</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>47.29</v>
+        <v>52.78</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=47.3); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-1.99)</t>
+          <t>RSI not pulled back (RSI=52.8); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-1.35)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>248.56</v>
+        <v>247.67</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>255.56</v>
+        <v>255.59</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>240.03</v>
+        <v>240.12</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>37.64</v>
+        <v>37.56</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-1.61)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-2.11)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>211.28</v>
+        <v>215.34</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>213</v>
+        <v>213.39</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>197.42</v>
+        <v>197.6</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>48.92</v>
+        <v>54.12</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=48.9)</t>
+          <t>RSI not pulled back (RSI=54.1)</t>
         </is>
       </c>
     </row>
@@ -730,25 +730,25 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>666.03</v>
+        <v>676.4299999999999</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>603.87</v>
+        <v>605.17</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>623.01</v>
+        <v>623.25</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>83.65000000000001</v>
+        <v>84.13</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H7" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=83.6); volume elevated on pullback (ratio=1.15)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=84.1)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>358.97</v>
+        <v>361.35</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>352.59</v>
+        <v>351.71</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>398.33</v>
+        <v>397.99</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>53.63</v>
+        <v>56.32</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=53.6); SMA50 flattening/falling (trend weakening); pullback too deep (15.6% off high)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=56.3); SMA50 flattening/falling (trend weakening); pullback too deep (15.0% off high)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -37,6 +37,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,16 +517,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>333.13</v>
+        <v>335.41</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>319.16</v>
+        <v>319.59</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>285.38</v>
+        <v>285.67</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>67.91</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +535,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,53 +545,49 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=67.9)</t>
+          <t>RSI not pulled back (RSI=68.6)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>493.77</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>459.76</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>430</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>48.57</v>
-      </c>
-      <c r="G3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>RSI not pulled back (RSI=48.6)</t>
-        </is>
-      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>494.83</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>461.94</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>430.01</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="G3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -598,16 +601,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>345.19</v>
+        <v>344.99</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>345.91</v>
+        <v>345.53</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>336.78</v>
+        <v>336.9</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>52.78</v>
+        <v>53.56</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +619,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +629,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=52.8); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-1.35)</t>
+          <t>RSI not pulled back (RSI=53.6); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-1.11)</t>
         </is>
       </c>
     </row>
@@ -642,16 +645,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>247.67</v>
+        <v>251.12</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>255.59</v>
+        <v>255.7</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>240.12</v>
+        <v>240.2</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>37.56</v>
+        <v>45.2</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,53 +673,49 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-2.11)</t>
+          <t>RSI not pulled back (RSI=45.2); MACD below zero line (momentum turned negative, MACD=-2.29)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>215.34</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>213.39</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>197.6</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>54.12</v>
-      </c>
-      <c r="G6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>RSI not pulled back (RSI=54.1)</t>
-        </is>
-      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>218.82</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>213.66</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>197.8</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>42.17</v>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -730,16 +729,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>676.4299999999999</v>
+        <v>678.29</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>605.17</v>
+        <v>606.61</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>623.25</v>
+        <v>623.39</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>84.13</v>
+        <v>87.28</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +747,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +757,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=84.1)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=87.3)</t>
         </is>
       </c>
     </row>
@@ -774,16 +773,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>361.35</v>
+        <v>367.67</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>351.71</v>
+        <v>351.12</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>397.99</v>
+        <v>397.66</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>56.32</v>
+        <v>55.35</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +791,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>15</v>
+        <v>13.6</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +801,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=56.3); SMA50 flattening/falling (trend weakening); pullback too deep (15.0% off high)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=55.3); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>335.41</v>
+        <v>334.57</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>319.59</v>
+        <v>319.99</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>285.67</v>
+        <v>285.94</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>68.56999999999999</v>
+        <v>63.52</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -535,7 +535,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -545,7 +545,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=68.6)</t>
+          <t>RSI not pulled back (RSI=63.5)</t>
         </is>
       </c>
     </row>
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>494.83</v>
+        <v>493.38</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>461.94</v>
+        <v>464.19</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>430.01</v>
+        <v>430.07</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>44.34</v>
+        <v>38.7</v>
       </c>
       <c r="G3" s="2" t="b">
         <v>1</v>
@@ -579,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J3" s="2" t="b">
         <v>1</v>
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>344.99</v>
+        <v>350</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>345.53</v>
+        <v>345.41</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>336.9</v>
+        <v>337.09</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>53.56</v>
+        <v>52.88</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -619,7 +619,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -629,7 +629,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=53.6); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-1.11)</t>
+          <t>RSI not pulled back (RSI=52.9); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.22)</t>
         </is>
       </c>
     </row>
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>251.12</v>
+        <v>253.76</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>255.7</v>
+        <v>255.84</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>240.2</v>
+        <v>240.3</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45.2</v>
+        <v>36.22</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>11.6</v>
+        <v>10.7</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -673,49 +673,53 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=45.2); MACD below zero line (momentum turned negative, MACD=-2.29)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-2.09)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>218.82</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>213.66</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>197.8</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>42.17</v>
-      </c>
-      <c r="G6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>219.55</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>214.01</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>198.01</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="G6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>RSI not pulled back (RSI=52.4)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -729,16 +733,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>678.29</v>
+        <v>669.99</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>606.61</v>
+        <v>607.46</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>623.39</v>
+        <v>623.5700000000001</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>87.28</v>
+        <v>80.02</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -747,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -757,7 +761,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=87.3)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=80.0)</t>
         </is>
       </c>
     </row>
@@ -773,16 +777,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>367.67</v>
+        <v>363.4</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>351.12</v>
+        <v>350.23</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>397.66</v>
+        <v>397.32</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>55.35</v>
+        <v>56.34</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -791,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>13.6</v>
+        <v>14.6</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -801,7 +805,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=55.3); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=56.3); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>334.57</v>
+        <v>338.85</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>319.99</v>
+        <v>320.5</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>285.94</v>
+        <v>286.21</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>63.52</v>
+        <v>70.64</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -535,7 +535,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -545,7 +545,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=63.5)</t>
+          <t>RSI not pulled back (RSI=70.6)</t>
         </is>
       </c>
     </row>
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>493.38</v>
+        <v>497.87</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>464.19</v>
+        <v>466.47</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>430.07</v>
+        <v>430.13</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>38.7</v>
+        <v>44.56</v>
       </c>
       <c r="G3" s="2" t="b">
         <v>1</v>
@@ -579,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="J3" s="2" t="b">
         <v>1</v>
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>350</v>
+        <v>356.48</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>345.41</v>
+        <v>345.39</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>337.09</v>
+        <v>337.29</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>52.88</v>
+        <v>63.93</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -619,17 +619,17 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>7.3</v>
+        <v>5.5</v>
       </c>
       <c r="J4" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=52.9); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.22)</t>
+          <t>RSI not pulled back (RSI=63.9); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>253.76</v>
+        <v>258.44</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>255.84</v>
+        <v>256.1</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>240.3</v>
+        <v>240.42</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>36.22</v>
+        <v>48.49</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>10.7</v>
+        <v>9</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-2.09)</t>
+          <t>RSI not pulled back (RSI=48.5); MACD below zero line (momentum turned negative, MACD=-1.54)</t>
         </is>
       </c>
     </row>
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>219.55</v>
+        <v>227.43</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>214.01</v>
+        <v>214.4</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>198.01</v>
+        <v>198.25</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>52.38</v>
+        <v>56.65</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=52.4)</t>
+          <t>RSI not pulled back (RSI=56.7)</t>
         </is>
       </c>
     </row>
@@ -733,25 +733,25 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>669.99</v>
+        <v>746.76</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>607.46</v>
+        <v>608.9299999999999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>623.5700000000001</v>
+        <v>624.05</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>80.02</v>
+        <v>87.47</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H7" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=80.0)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=87.5); volume elevated on pullback (ratio=1.15)</t>
         </is>
       </c>
     </row>
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>363.4</v>
+        <v>374.38</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>350.23</v>
+        <v>349.58</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>397.32</v>
+        <v>397.05</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>56.34</v>
+        <v>53.05</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>14.6</v>
+        <v>12</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -805,7 +805,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=56.3); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=53.0); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -37,12 +37,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,10 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>338.85</v>
+        <v>341.55</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>320.5</v>
+        <v>320.99</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>286.21</v>
+        <v>286.5</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>70.64</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -535,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -545,49 +538,53 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=70.6)</t>
+          <t>RSI not pulled back (RSI=67.2)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>497.87</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>466.47</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>430.13</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>44.56</v>
-      </c>
-      <c r="G3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>497.04</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>468.68</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>430.26</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="G3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>RSI not pulled back (RSI=47.8)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -601,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>356.48</v>
+        <v>352.62</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>345.39</v>
+        <v>345.37</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>337.29</v>
+        <v>337.46</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>63.93</v>
+        <v>65.16</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -619,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
@@ -629,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=63.9); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=65.2); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -645,25 +642,25 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>258.44</v>
+        <v>254.53</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256.1</v>
+        <v>256.25</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>240.42</v>
+        <v>240.53</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>48.49</v>
+        <v>49.55</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H5" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>9</v>
+        <v>10.4</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -673,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=48.5); MACD below zero line (momentum turned negative, MACD=-1.54)</t>
+          <t>RSI not pulled back (RSI=49.5); volume elevated on pullback (ratio=1.10); MACD below zero line (momentum turned negative, MACD=-1.40)</t>
         </is>
       </c>
     </row>
@@ -689,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>227.43</v>
+        <v>229.46</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>214.4</v>
+        <v>214.92</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>198.25</v>
+        <v>198.5</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>56.65</v>
+        <v>62.13</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -707,17 +704,17 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=56.7)</t>
+          <t>RSI not pulled back (RSI=62.1)</t>
         </is>
       </c>
     </row>
@@ -733,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>746.76</v>
+        <v>743.23</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>608.9299999999999</v>
+        <v>610.09</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>624.05</v>
+        <v>624.0700000000001</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>87.47</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -761,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=87.5); volume elevated on pullback (ratio=1.15)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=87.0); volume elevated on pullback (ratio=1.24)</t>
         </is>
       </c>
     </row>
@@ -777,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>374.38</v>
+        <v>378.41</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>349.58</v>
+        <v>349.27</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>397.05</v>
+        <v>396.71</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>53.05</v>
+        <v>61.42</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -795,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -805,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=53.0); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=61.4); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>341.55</v>
+        <v>337.05</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>320.99</v>
+        <v>320.9</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>286.5</v>
+        <v>286.48</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>67.20999999999999</v>
+        <v>62.65</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=67.2)</t>
+          <t>RSI not pulled back (RSI=62.7)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>497.04</v>
+        <v>499.41</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>468.68</v>
+        <v>468.73</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>430.26</v>
+        <v>430.27</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>47.75</v>
+        <v>49.07</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=47.8)</t>
+          <t>RSI not pulled back (RSI=49.1)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>352.62</v>
+        <v>338.11</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>345.37</v>
+        <v>345.08</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>337.46</v>
+        <v>337.38</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>65.16</v>
+        <v>52.25</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>6.6</v>
+        <v>10.4</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=65.2); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=52.3); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>254.53</v>
+        <v>248.22</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256.25</v>
+        <v>256.12</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>240.53</v>
+        <v>240.5</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>49.55</v>
+        <v>43.22</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>10.4</v>
+        <v>12.6</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=49.5); volume elevated on pullback (ratio=1.10); MACD below zero line (momentum turned negative, MACD=-1.40)</t>
+          <t>volume elevated on pullback (ratio=1.11); MACD below zero line (momentum turned negative, MACD=-1.91)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>229.46</v>
+        <v>224.61</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>214.92</v>
+        <v>214.83</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>198.5</v>
+        <v>198.48</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>62.13</v>
+        <v>57.23</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=62.1)</t>
+          <t>RSI not pulled back (RSI=57.2)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>743.23</v>
+        <v>748.75</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>610.09</v>
+        <v>610.2</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>624.0700000000001</v>
+        <v>624.09</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>86.95999999999999</v>
+        <v>87.27</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=87.0); volume elevated on pullback (ratio=1.24)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=87.3); volume elevated on pullback (ratio=1.25)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>378.41</v>
+        <v>378.97</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>349.27</v>
+        <v>349.28</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>396.71</v>
+        <v>396.72</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>61.42</v>
+        <v>61.64</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=61.4); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=61.6); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>337.05</v>
+        <v>337.22</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>320.9</v>
+        <v>321.61</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>286.48</v>
+        <v>287.07</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>62.65</v>
+        <v>59.92</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=62.7)</t>
+          <t>RSI not pulled back (RSI=59.9)</t>
         </is>
       </c>
     </row>
@@ -554,25 +554,25 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>499.41</v>
+        <v>495.39</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>468.73</v>
+        <v>473.04</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>430.27</v>
+        <v>430.46</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>49.07</v>
+        <v>40.55</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H3" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=49.1)</t>
+          <t>volume elevated on pullback (ratio=1.12)</t>
         </is>
       </c>
     </row>
@@ -598,25 +598,25 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>338.11</v>
+        <v>341.36</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>345.08</v>
+        <v>344.32</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>337.38</v>
+        <v>337.66</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>52.25</v>
+        <v>49.36</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H4" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=52.3); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=49.4); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.19)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>248.22</v>
+        <v>248.68</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256.12</v>
+        <v>256.17</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>240.5</v>
+        <v>240.73</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>43.22</v>
+        <v>38.64</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>volume elevated on pullback (ratio=1.11); MACD below zero line (momentum turned negative, MACD=-1.91)</t>
+          <t>volume elevated on pullback (ratio=1.15); MACD below zero line (momentum turned negative, MACD=-1.94)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>224.61</v>
+        <v>223.92</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>214.83</v>
+        <v>215.42</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>198.48</v>
+        <v>198.92</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>57.23</v>
+        <v>45.13</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=57.2)</t>
+          <t>RSI not pulled back (RSI=45.1)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>748.75</v>
+        <v>770.16</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>610.2</v>
+        <v>613.42</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>624.09</v>
+        <v>624.95</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>87.27</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=87.3); volume elevated on pullback (ratio=1.25)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=85.2); volume elevated on pullback (ratio=1.46)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>378.97</v>
+        <v>380.87</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>349.28</v>
+        <v>348.69</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>396.72</v>
+        <v>395.97</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>61.64</v>
+        <v>52.82</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=61.6); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=52.8); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -37,6 +37,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,16 +517,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>337.22</v>
+        <v>340.14</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>321.61</v>
+        <v>321.72</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>287.07</v>
+        <v>287.38</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>59.92</v>
+        <v>73.84</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +535,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +545,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=59.9)</t>
+          <t>RSI not pulled back (RSI=73.8)</t>
         </is>
       </c>
     </row>
@@ -554,25 +561,25 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>495.39</v>
+        <v>516.05</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>473.04</v>
+        <v>475.4</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>430.46</v>
+        <v>430.61</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>40.55</v>
+        <v>59.83</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H3" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +589,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>volume elevated on pullback (ratio=1.12)</t>
+          <t>RSI not pulled back (RSI=59.8)</t>
         </is>
       </c>
     </row>
@@ -598,25 +605,25 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>341.36</v>
+        <v>344.17</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>344.32</v>
+        <v>344.14</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>337.66</v>
+        <v>337.82</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>49.36</v>
+        <v>54.16</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H4" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
@@ -626,7 +633,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=49.4); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.19)</t>
+          <t>RSI not pulled back (RSI=54.2); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -642,25 +649,25 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>248.68</v>
+        <v>250.06</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256.17</v>
+        <v>256.18</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>240.73</v>
+        <v>240.85</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>38.64</v>
+        <v>40.57</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H5" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,53 +677,49 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>volume elevated on pullback (ratio=1.15); MACD below zero line (momentum turned negative, MACD=-1.94)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-1.97)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>223.92</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>215.42</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>198.92</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>45.13</v>
-      </c>
-      <c r="G6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>RSI not pulled back (RSI=45.1)</t>
-        </is>
-      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>224.83</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>215.79</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>199.13</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -730,16 +733,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>770.16</v>
+        <v>748.84</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>613.42</v>
+        <v>615.26</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>624.95</v>
+        <v>625.41</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>85.15000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +761,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=85.2); volume elevated on pullback (ratio=1.46)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=75.7); volume elevated on pullback (ratio=1.42)</t>
         </is>
       </c>
     </row>
@@ -774,16 +777,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>380.87</v>
+        <v>373.35</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>348.69</v>
+        <v>348.27</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>395.97</v>
+        <v>395.63</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>52.82</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>10.4</v>
+        <v>12.2</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +805,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=52.8); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=65.2); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -37,12 +37,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,10 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>340.14</v>
+        <v>338.32</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>321.72</v>
+        <v>321.84</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>287.38</v>
+        <v>287.7</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>73.84</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -535,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -545,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=73.8)</t>
+          <t>RSI not pulled back (RSI=76.2)</t>
         </is>
       </c>
     </row>
@@ -561,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>516.05</v>
+        <v>509.11</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>475.4</v>
+        <v>477.72</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>430.61</v>
+        <v>430.71</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>59.83</v>
+        <v>58.96</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -579,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -589,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=59.8)</t>
+          <t>RSI not pulled back (RSI=59.0)</t>
         </is>
       </c>
     </row>
@@ -605,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>344.17</v>
+        <v>342.51</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>344.14</v>
+        <v>344.05</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>337.82</v>
+        <v>337.95</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>54.16</v>
+        <v>52.98</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -623,17 +616,17 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=54.2); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=53.0); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.02)</t>
         </is>
       </c>
     </row>
@@ -649,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>250.06</v>
+        <v>246.26</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256.18</v>
+        <v>256.16</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>240.85</v>
+        <v>240.94</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>40.57</v>
+        <v>38.43</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -667,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>12</v>
+        <v>13.3</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -677,49 +670,53 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-1.97)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-2.34)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>224.83</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>215.79</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>199.13</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>43.66</v>
-      </c>
-      <c r="G6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2" t="b">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>228.75</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>216.32</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>199.35</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="G6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>RSI not pulled back (RSI=54.0)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -733,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>748.84</v>
+        <v>714.9299999999999</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>615.26</v>
+        <v>616.71</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>625.41</v>
+        <v>625.73</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>75.73</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -751,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>3.7</v>
+        <v>8.1</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -761,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=75.7); volume elevated on pullback (ratio=1.42)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=67.7); volume elevated on pullback (ratio=1.22)</t>
         </is>
       </c>
     </row>
@@ -777,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>373.35</v>
+        <v>357.89</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>348.27</v>
+        <v>347.79</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>395.63</v>
+        <v>395.19</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>65.15000000000001</v>
+        <v>42.1</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -795,17 +792,17 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>12.2</v>
+        <v>15.8</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=65.2); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening); pullback too deep (15.8% off high)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>338.32</v>
+        <v>331.46</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>321.84</v>
+        <v>321.94</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>287.7</v>
+        <v>287.96</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>76.15000000000001</v>
+        <v>66.72</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,17 +528,17 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=76.2)</t>
+          <t>RSI not pulled back (RSI=66.7)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>509.11</v>
+        <v>507.09</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>477.72</v>
+        <v>479.84</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>430.71</v>
+        <v>430.87</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>58.96</v>
+        <v>59.16</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=59.0)</t>
+          <t>RSI not pulled back (RSI=59.2)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>342.51</v>
+        <v>339.76</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>344.05</v>
+        <v>343.82</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>337.95</v>
+        <v>338.05</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>52.98</v>
+        <v>57.03</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,17 +616,17 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K4" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=53.0); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.02)</t>
+          <t>RSI not pulled back (RSI=57.0); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.34)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>246.26</v>
+        <v>247.15</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256.16</v>
+        <v>256.1</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>240.94</v>
+        <v>241.02</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>38.43</v>
+        <v>43.87</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-2.34)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-2.52)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>228.75</v>
+        <v>228.04</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>216.32</v>
+        <v>216.82</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>199.35</v>
+        <v>199.57</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>54</v>
+        <v>55.81</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=54.0)</t>
+          <t>RSI not pulled back (RSI=55.8)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>714.9299999999999</v>
+        <v>731.33</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>616.71</v>
+        <v>618.4400000000001</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>625.73</v>
+        <v>626.15</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>67.68000000000001</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>8.1</v>
+        <v>5.9</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=67.7); volume elevated on pullback (ratio=1.22)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=64.9); volume elevated on pullback (ratio=1.14)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>357.89</v>
+        <v>354.03</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>347.79</v>
+        <v>347.47</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>395.19</v>
+        <v>394.7</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>42.1</v>
+        <v>39.94</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening); pullback too deep (15.8% off high)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening); pullback too deep (16.8% off high)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>331.46</v>
+        <v>336.63</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>321.94</v>
+        <v>322.09</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>287.96</v>
+        <v>288.25</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>66.72</v>
+        <v>60.87</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=66.7)</t>
+          <t>RSI not pulled back (RSI=60.9)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>507.09</v>
+        <v>518.4</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>479.84</v>
+        <v>482.3</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>430.87</v>
+        <v>431.07</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>59.16</v>
+        <v>64.25</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,17 +572,17 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=59.2)</t>
+          <t>RSI not pulled back (RSI=64.3)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>339.76</v>
+        <v>349.3</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>343.82</v>
+        <v>343.89</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>338.05</v>
+        <v>338.24</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>57.03</v>
+        <v>61.92</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,17 +616,17 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="J4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="K4" s="1" t="b">
-        <v>1</v>
-      </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=57.0); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.34)</t>
+          <t>RSI not pulled back (RSI=61.9); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>247.15</v>
+        <v>250.78</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256.1</v>
+        <v>256.15</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>241.02</v>
+        <v>241.12</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>43.87</v>
+        <v>48.79</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-2.52)</t>
+          <t>RSI not pulled back (RSI=48.8); MACD below zero line (momentum turned negative, MACD=-2.37)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>228.04</v>
+        <v>230.74</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>216.82</v>
+        <v>217.28</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>199.57</v>
+        <v>199.82</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>55.81</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=55.8)</t>
+          <t>RSI not pulled back (RSI=65.8)</t>
         </is>
       </c>
     </row>
@@ -730,25 +730,25 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>731.33</v>
+        <v>734.15</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>618.4400000000001</v>
+        <v>620.41</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>626.15</v>
+        <v>626.6</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>64.84999999999999</v>
+        <v>66.98</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H7" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=64.9); volume elevated on pullback (ratio=1.14)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=67.0)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>354.03</v>
+        <v>353.33</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>347.47</v>
+        <v>346.93</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>394.7</v>
+        <v>394.22</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>39.94</v>
+        <v>42.24</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening); pullback too deep (16.8% off high)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening); pullback too deep (15.8% off high)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>336.63</v>
+        <v>329.85</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>322.09</v>
+        <v>322.1</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>288.25</v>
+        <v>288.5</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>60.87</v>
+        <v>46.99</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=60.9)</t>
+          <t>RSI not pulled back (RSI=47.0)</t>
         </is>
       </c>
     </row>
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>518.4</v>
+        <v>516.38</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>482.3</v>
+        <v>484.73</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>431.07</v>
+        <v>431.25</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>64.25</v>
+        <v>62.08</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H3" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>0</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=64.3)</t>
+          <t>RSI not pulled back (RSI=62.1); volume elevated on pullback (ratio=1.11)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>349.3</v>
+        <v>338.85</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>343.89</v>
+        <v>343.73</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>338.24</v>
+        <v>338.37</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>61.92</v>
+        <v>50.27</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,17 +616,17 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>7.4</v>
+        <v>10.2</v>
       </c>
       <c r="J4" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=61.9); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=50.3); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.56)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>250.78</v>
+        <v>249.49</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256.15</v>
+        <v>256.21</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>241.12</v>
+        <v>241.22</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>48.79</v>
+        <v>40.82</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=48.8); MACD below zero line (momentum turned negative, MACD=-2.37)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-2.39)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>230.74</v>
+        <v>231.74</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>217.28</v>
+        <v>217.63</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>199.82</v>
+        <v>200.09</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>65.84999999999999</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=65.8)</t>
+          <t>RSI not pulled back (RSI=66.8)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>734.15</v>
+        <v>726.77</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>620.41</v>
+        <v>622.23</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>626.6</v>
+        <v>626.98</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>66.98</v>
+        <v>64.53</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=67.0)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=64.5)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>353.33</v>
+        <v>356.86</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>346.93</v>
+        <v>346.62</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>394.22</v>
+        <v>393.72</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>42.24</v>
+        <v>43.65</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>15.8</v>
+        <v>15</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening); pullback too deep (15.8% off high)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>329.85</v>
+        <v>332.95</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>322.1</v>
+        <v>322.34</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>288.5</v>
+        <v>288.8</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46.99</v>
+        <v>49.84</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=47.0)</t>
+          <t>RSI not pulled back (RSI=49.8)</t>
         </is>
       </c>
     </row>
@@ -554,25 +554,25 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>516.38</v>
+        <v>515.0599999999999</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>484.73</v>
+        <v>487.34</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>431.25</v>
+        <v>431.44</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>62.08</v>
+        <v>56.44</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H3" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=62.1); volume elevated on pullback (ratio=1.11)</t>
+          <t>RSI not pulled back (RSI=56.4)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>338.85</v>
+        <v>343.69</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>343.73</v>
+        <v>344.24</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>338.37</v>
+        <v>338.55</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>50.27</v>
+        <v>45.19</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>10.2</v>
+        <v>8.9</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=50.3); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.56)</t>
+          <t>RSI not pulled back (RSI=45.2); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.49)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>249.49</v>
+        <v>250.82</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256.21</v>
+        <v>256.53</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>241.22</v>
+        <v>241.36</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>40.82</v>
+        <v>46.57</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>12.2</v>
+        <v>11.7</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-2.39)</t>
+          <t>RSI not pulled back (RSI=46.6); MACD below zero line (momentum turned negative, MACD=-2.25)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>231.74</v>
+        <v>234.68</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>217.63</v>
+        <v>218.13</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>200.09</v>
+        <v>200.38</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>66.81999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=66.8)</t>
+          <t>RSI not pulled back (RSI=83.3)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>726.77</v>
+        <v>728.99</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>622.23</v>
+        <v>624.6799999999999</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>626.98</v>
+        <v>627.39</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>64.53</v>
+        <v>62.41</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,17 +748,17 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=64.5)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=62.4)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>356.86</v>
+        <v>371.59</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>346.62</v>
+        <v>347.6</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>393.72</v>
+        <v>393.19</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>43.65</v>
+        <v>58.17</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>15</v>
+        <v>8.9</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=58.2); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>332.95</v>
+        <v>333.49</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>322.34</v>
+        <v>322.3</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>288.8</v>
+        <v>289.41</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>49.84</v>
+        <v>51.32</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=49.8)</t>
+          <t>RSI not pulled back (RSI=51.3)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>515.0599999999999</v>
+        <v>530.5599999999999</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>487.34</v>
+        <v>493.12</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>431.44</v>
+        <v>432</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>56.44</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=56.4)</t>
+          <t>RSI not pulled back (RSI=76.7)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>343.69</v>
+        <v>348.44</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>344.24</v>
+        <v>345.21</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>338.55</v>
+        <v>339.01</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45.19</v>
+        <v>54.84</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,17 +616,17 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J4" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=45.2); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.49)</t>
+          <t>RSI not pulled back (RSI=54.8); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>250.82</v>
+        <v>256.2</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256.53</v>
+        <v>257.43</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>241.36</v>
+        <v>241.68</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46.57</v>
+        <v>63.58</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,17 +660,17 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>11.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="K5" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=46.6); MACD below zero line (momentum turned negative, MACD=-2.25)</t>
+          <t>RSI not pulled back (RSI=63.6); MACD below zero line (momentum turned negative, MACD=-1.35)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>234.68</v>
+        <v>240.2</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>218.13</v>
+        <v>219.64</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>200.38</v>
+        <v>201.04</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>83.31</v>
+        <v>84.44</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=83.3)</t>
+          <t>RSI not pulled back (RSI=84.4)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>728.99</v>
+        <v>742.83</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>624.6799999999999</v>
+        <v>630.6</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>627.39</v>
+        <v>628.29</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>62.41</v>
+        <v>63.29</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=62.4)</t>
+          <t>RSI not pulled back (RSI=63.3)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>371.59</v>
+        <v>379.46</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>347.6</v>
+        <v>350.3</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>393.19</v>
+        <v>392.19</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>58.17</v>
+        <v>63.17</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,17 +792,17 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=58.2); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=63.2); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>333.49</v>
+        <v>336.96</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>322.3</v>
+        <v>322.24</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>289.41</v>
+        <v>289.73</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>51.32</v>
+        <v>49.96</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=51.3)</t>
+          <t>RSI not pulled back (RSI=50.0)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>530.5599999999999</v>
+        <v>530.8200000000001</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>493.12</v>
+        <v>495.86</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>432</v>
+        <v>432.25</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>76.70999999999999</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=76.7)</t>
+          <t>RSI not pulled back (RSI=74.3)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>348.44</v>
+        <v>349.02</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>345.21</v>
+        <v>345.51</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>339.01</v>
+        <v>339.24</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>54.84</v>
+        <v>51.58</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=54.8); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=51.6); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>256.2</v>
+        <v>259.58</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>257.43</v>
+        <v>258</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>241.68</v>
+        <v>241.85</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>63.58</v>
+        <v>61.69</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=63.6); MACD below zero line (momentum turned negative, MACD=-1.35)</t>
+          <t>RSI not pulled back (RSI=61.7); MACD below zero line (momentum turned negative, MACD=-0.59)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>240.2</v>
+        <v>236.71</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>219.64</v>
+        <v>220.42</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>201.04</v>
+        <v>201.35</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>84.44</v>
+        <v>75.31</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=84.4)</t>
+          <t>RSI not pulled back (RSI=75.3)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>742.83</v>
+        <v>722.91</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>630.6</v>
+        <v>633.12</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>628.29</v>
+        <v>628.58</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>63.29</v>
+        <v>57.54</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=63.3)</t>
+          <t>RSI not pulled back (RSI=57.5)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>379.46</v>
+        <v>377.35</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>350.3</v>
+        <v>351.73</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>392.19</v>
+        <v>391.66</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>63.17</v>
+        <v>57.18</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=63.2); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=57.2); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>336.96</v>
+        <v>340.73</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>322.24</v>
+        <v>322.29</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>289.73</v>
+        <v>290.07</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>49.96</v>
+        <v>55.4</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=50.0)</t>
+          <t>RSI not pulled back (RSI=55.4)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>530.8200000000001</v>
+        <v>521.4299999999999</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>495.86</v>
+        <v>498.47</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>432.25</v>
+        <v>432.43</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>74.26000000000001</v>
+        <v>69.34</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=74.3)</t>
+          <t>RSI not pulled back (RSI=69.3)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>349.02</v>
+        <v>348.15</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>345.51</v>
+        <v>345.77</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>339.24</v>
+        <v>339.46</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>51.58</v>
+        <v>48.74</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=51.6); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=48.7); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>259.58</v>
+        <v>254.69</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>258</v>
+        <v>258.57</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>241.85</v>
+        <v>241.98</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>61.69</v>
+        <v>51.26</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>8.6</v>
+        <v>10.3</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=61.7); MACD below zero line (momentum turned negative, MACD=-0.59)</t>
+          <t>RSI not pulled back (RSI=51.3); MACD below zero line (momentum turned negative, MACD=-0.36)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>236.71</v>
+        <v>230.41</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>220.42</v>
+        <v>221.25</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>201.35</v>
+        <v>201.6</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>75.31</v>
+        <v>60.8</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=75.3)</t>
+          <t>RSI not pulled back (RSI=60.8)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>722.91</v>
+        <v>719.64</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>633.12</v>
+        <v>635.77</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>628.58</v>
+        <v>628.88</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>57.54</v>
+        <v>60.49</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=57.5)</t>
+          <t>RSI not pulled back (RSI=60.5)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>377.35</v>
+        <v>371.91</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>351.73</v>
+        <v>353.21</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>391.66</v>
+        <v>391.12</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>57.18</v>
+        <v>54.71</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=57.2); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=54.7); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -37,6 +37,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,16 +517,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>340.73</v>
+        <v>336.73</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>322.29</v>
+        <v>322.36</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>290.07</v>
+        <v>290.4</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>55.4</v>
+        <v>47.39</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +535,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +545,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=55.4)</t>
+          <t>RSI not pulled back (RSI=47.4)</t>
         </is>
       </c>
     </row>
@@ -554,16 +561,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>521.4299999999999</v>
+        <v>534.65</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>498.47</v>
+        <v>500.18</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>432.43</v>
+        <v>432.7</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>69.34</v>
+        <v>72.17</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +589,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=69.3)</t>
+          <t>RSI not pulled back (RSI=72.2)</t>
         </is>
       </c>
     </row>
@@ -598,16 +605,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>348.15</v>
+        <v>351.41</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>345.77</v>
+        <v>346.13</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>339.46</v>
+        <v>339.67</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>48.74</v>
+        <v>46.63</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +623,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
@@ -626,7 +633,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=48.7); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=46.6); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -642,16 +649,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>254.69</v>
+        <v>260.95</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>258.57</v>
+        <v>259.07</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>241.98</v>
+        <v>242.14</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>51.26</v>
+        <v>53</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,17 +667,17 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>10.3</v>
+        <v>8.1</v>
       </c>
       <c r="J5" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=51.3); MACD below zero line (momentum turned negative, MACD=-0.36)</t>
+          <t>RSI not pulled back (RSI=53.0)</t>
         </is>
       </c>
     </row>
@@ -686,16 +693,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>230.41</v>
+        <v>229.65</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>221.25</v>
+        <v>221.95</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>201.6</v>
+        <v>201.83</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>60.8</v>
+        <v>53.41</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +711,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,53 +721,49 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=60.8)</t>
+          <t>RSI not pulled back (RSI=53.4)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>719.64</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>635.77</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>628.88</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="G7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>RSI not pulled back (RSI=60.5)</t>
-        </is>
-      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>717.02</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>639.37</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>629.17</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -774,25 +777,25 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>371.91</v>
+        <v>384</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>353.21</v>
+        <v>354.77</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>391.12</v>
+        <v>390.61</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>54.71</v>
+        <v>55.72</v>
       </c>
       <c r="G8" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>6.1</v>
+        <v>3.1</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +805,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=54.7); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=55.7)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -37,12 +37,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,10 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>336.73</v>
+        <v>340.97</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>322.36</v>
+        <v>323</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>290.4</v>
+        <v>290.75</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>47.39</v>
+        <v>51.3</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -535,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -545,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=47.4)</t>
+          <t>RSI not pulled back (RSI=51.3)</t>
         </is>
       </c>
     </row>
@@ -561,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>534.65</v>
+        <v>541.15</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>500.18</v>
+        <v>501.73</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>432.7</v>
+        <v>432.99</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>72.17</v>
+        <v>77.88</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -589,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=72.2)</t>
+          <t>RSI not pulled back (RSI=77.9)</t>
         </is>
       </c>
     </row>
@@ -605,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>351.41</v>
+        <v>352.72</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>346.13</v>
+        <v>346.08</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>339.67</v>
+        <v>339.86</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46.63</v>
+        <v>51.55</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -623,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
@@ -633,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=46.6); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=51.6); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -649,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>260.95</v>
+        <v>259.53</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>259.07</v>
+        <v>258.85</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>242.14</v>
+        <v>242.29</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>53</v>
+        <v>55.34</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -667,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
@@ -677,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=53.0)</t>
+          <t>RSI not pulled back (RSI=55.3)</t>
         </is>
       </c>
     </row>
@@ -693,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>229.65</v>
+        <v>226.32</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>221.95</v>
+        <v>222.46</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>201.83</v>
+        <v>202.02</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>53.41</v>
+        <v>46.37</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -711,59 +704,63 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=53.4)</t>
+          <t>RSI not pulled back (RSI=46.4)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>717.02</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>639.37</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>629.17</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>43.49</v>
-      </c>
-      <c r="G7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>742.96</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>643.13</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>629.58</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>51.56</v>
+      </c>
+      <c r="G7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>RSI not pulled back (RSI=51.6)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -777,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>384</v>
+        <v>378.03</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>354.77</v>
+        <v>356.08</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>390.61</v>
+        <v>390.07</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>55.72</v>
+        <v>49.43</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -795,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -805,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=55.7)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=49.4)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>340.97</v>
+        <v>340.85</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>323</v>
+        <v>323.76</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>290.75</v>
+        <v>291.09</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>51.3</v>
+        <v>54.34</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=51.3)</t>
+          <t>RSI not pulled back (RSI=54.3)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>541.15</v>
+        <v>545.24</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>501.73</v>
+        <v>502.9</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>432.99</v>
+        <v>433.29</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>77.88</v>
+        <v>78.3</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=77.9)</t>
+          <t>RSI not pulled back (RSI=78.3)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>352.72</v>
+        <v>355.06</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>346.08</v>
+        <v>345.71</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>339.86</v>
+        <v>340.07</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>51.55</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=51.6); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=71.9); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>259.53</v>
+        <v>259.7</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>258.85</v>
+        <v>258.37</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>242.29</v>
+        <v>242.43</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>55.34</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=55.3)</t>
+          <t>RSI not pulled back (RSI=64.1)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>226.32</v>
+        <v>227.9</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>222.46</v>
+        <v>222.89</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>202.02</v>
+        <v>202.22</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46.37</v>
+        <v>53.59</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=46.4)</t>
+          <t>RSI not pulled back (RSI=53.6)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>742.96</v>
+        <v>765.58</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>643.13</v>
+        <v>646.65</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>629.58</v>
+        <v>630.08</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>51.56</v>
+        <v>54.9</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=51.6)</t>
+          <t>RSI not pulled back (RSI=54.9)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>378.03</v>
+        <v>375.66</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>356.08</v>
+        <v>357.15</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>390.07</v>
+        <v>389.52</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>49.43</v>
+        <v>47.1</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=49.4)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=47.1)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -37,6 +37,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,16 +517,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>340.85</v>
+        <v>342.04</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>323.76</v>
+        <v>324.42</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>291.09</v>
+        <v>291.44</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>54.34</v>
+        <v>56.95</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,17 +535,17 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=54.3)</t>
+          <t>RSI not pulled back (RSI=57.0)</t>
         </is>
       </c>
     </row>
@@ -554,16 +561,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>545.24</v>
+        <v>535.34</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>502.9</v>
+        <v>503.74</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>433.29</v>
+        <v>433.54</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>78.3</v>
+        <v>72.66</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +589,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=78.3)</t>
+          <t>RSI not pulled back (RSI=72.7)</t>
         </is>
       </c>
     </row>
@@ -598,16 +605,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>355.06</v>
+        <v>348.21</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>345.71</v>
+        <v>345.1</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>340.07</v>
+        <v>340.24</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>71.90000000000001</v>
+        <v>57.48</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +623,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>5.9</v>
+        <v>7.7</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
@@ -626,7 +633,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=71.9); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=57.5); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -642,16 +649,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>259.7</v>
+        <v>253.8</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>258.37</v>
+        <v>257.87</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>242.43</v>
+        <v>242.53</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>64.06999999999999</v>
+        <v>55.2</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +667,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>8.6</v>
+        <v>10.6</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
@@ -670,7 +677,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=64.1)</t>
+          <t>RSI not pulled back (RSI=55.2)</t>
         </is>
       </c>
     </row>
@@ -686,16 +693,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>227.9</v>
+        <v>221.39</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>222.89</v>
+        <v>223.09</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>202.22</v>
+        <v>202.37</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>53.59</v>
+        <v>46.03</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +711,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>4.7</v>
+        <v>7.5</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,53 +721,49 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=53.6)</t>
+          <t>RSI not pulled back (RSI=46.0)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>765.58</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>646.65</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>630.08</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="G7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>RSI not pulled back (RSI=54.9)</t>
-        </is>
-      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>735.91</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>649.5599999999999</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>630.4299999999999</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -774,16 +777,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>375.66</v>
+        <v>365.78</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>357.15</v>
+        <v>357.91</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>389.52</v>
+        <v>388.97</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>47.1</v>
+        <v>42.81</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -792,17 +795,17 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=47.1)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>342.04</v>
+        <v>344.29</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>324.42</v>
+        <v>325.11</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>291.44</v>
+        <v>291.8</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>56.95</v>
+        <v>53.92</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -545,7 +545,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=57.0)</t>
+          <t>RSI not pulled back (RSI=53.9)</t>
         </is>
       </c>
     </row>
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>535.34</v>
+        <v>539.15</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>503.74</v>
+        <v>504.76</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>433.54</v>
+        <v>433.8</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>72.66</v>
+        <v>66.09</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -579,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -589,7 +589,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=72.7)</t>
+          <t>RSI not pulled back (RSI=66.1)</t>
         </is>
       </c>
     </row>
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>348.21</v>
+        <v>349.28</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>345.1</v>
+        <v>344.83</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>340.24</v>
+        <v>340.42</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>57.48</v>
+        <v>56.74</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -623,7 +623,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=57.5); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=56.7); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>253.8</v>
+        <v>254.15</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>257.87</v>
+        <v>257.51</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>242.53</v>
+        <v>242.64</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>55.2</v>
+        <v>55.33</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -667,7 +667,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
@@ -677,93 +677,93 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=55.2)</t>
+          <t>RSI not pulled back (RSI=55.3)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>221.39</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>223.09</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>202.37</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>46.03</v>
-      </c>
-      <c r="G6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>RSI not pulled back (RSI=46.0)</t>
-        </is>
-      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>217.43</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>223.06</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>202.52</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>735.91</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>649.5599999999999</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>630.4299999999999</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>40.03</v>
-      </c>
-      <c r="G7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>742.09</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>652.67</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>630.87</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="G7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>RSI not pulled back (RSI=47.4)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>365.78</v>
+        <v>360.4</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>357.91</v>
+        <v>358.72</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>388.97</v>
+        <v>388.48</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>42.81</v>
+        <v>43.05</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -37,12 +37,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,10 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>344.29</v>
+        <v>342.86</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>325.11</v>
+        <v>325.68</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>291.8</v>
+        <v>292.14</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>53.92</v>
+        <v>55.72</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -545,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=53.9)</t>
+          <t>RSI not pulled back (RSI=55.7)</t>
         </is>
       </c>
     </row>
@@ -561,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>539.15</v>
+        <v>525.6</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>504.76</v>
+        <v>505.3</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>433.8</v>
+        <v>434.01</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>66.09</v>
+        <v>60.42</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -579,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -589,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=66.1)</t>
+          <t>RSI not pulled back (RSI=60.4)</t>
         </is>
       </c>
     </row>
@@ -605,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>349.28</v>
+        <v>341.22</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>344.83</v>
+        <v>344.5</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>340.42</v>
+        <v>340.56</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>56.74</v>
+        <v>48.36</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -623,17 +616,17 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>7.5</v>
+        <v>9.6</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K4" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=56.7); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=48.4); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -649,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>254.15</v>
+        <v>249.91</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>257.51</v>
+        <v>257.07</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>242.64</v>
+        <v>242.73</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>55.33</v>
+        <v>54.27</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -667,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
@@ -677,49 +670,53 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=55.3)</t>
+          <t>RSI not pulled back (RSI=54.3)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>217.43</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>223.06</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>202.52</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="G6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>215.6</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>222.99</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>202.66</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="G6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>MACD below zero line (momentum turned negative, MACD=-0.03)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -733,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>742.09</v>
+        <v>712.74</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>652.67</v>
+        <v>655.02</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>630.87</v>
+        <v>631.08</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>47.43</v>
+        <v>49.15</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -751,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>4.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -761,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=47.4)</t>
+          <t>RSI not pulled back (RSI=49.2)</t>
         </is>
       </c>
     </row>
@@ -777,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>360.4</v>
+        <v>352.57</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>358.72</v>
+        <v>359.42</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>388.48</v>
+        <v>387.98</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>43.05</v>
+        <v>46.84</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -795,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>5.8</v>
+        <v>7.9</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -805,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=46.8)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -37,6 +37,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,25 +517,25 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>342.86</v>
+        <v>343.13</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>325.68</v>
+        <v>326.3</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>292.14</v>
+        <v>292.5</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>55.72</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H2" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +545,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=55.7)</t>
+          <t>RSI not pulled back (RSI=72.2); volume elevated on pullback (ratio=1.16)</t>
         </is>
       </c>
     </row>
@@ -554,16 +561,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>525.6</v>
+        <v>534.51</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>505.3</v>
+        <v>506.07</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>434.01</v>
+        <v>434.3</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>60.42</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,17 +579,17 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=60.4)</t>
+          <t>RSI not pulled back (RSI=65.9)</t>
         </is>
       </c>
     </row>
@@ -598,16 +605,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>341.22</v>
+        <v>344.78</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>344.5</v>
+        <v>344.31</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>340.56</v>
+        <v>340.72</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>48.36</v>
+        <v>53.9</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +623,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
@@ -626,7 +633,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=48.4); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=53.9); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -642,16 +649,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>249.91</v>
+        <v>262.29</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>257.07</v>
+        <v>256.83</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>242.73</v>
+        <v>242.89</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>54.27</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +667,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>12</v>
+        <v>7.7</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
@@ -670,7 +677,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=54.3)</t>
+          <t>RSI not pulled back (RSI=64.0)</t>
         </is>
       </c>
     </row>
@@ -686,16 +693,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>215.6</v>
+        <v>217.23</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>222.99</v>
+        <v>222.83</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>202.66</v>
+        <v>202.81</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>34.11</v>
+        <v>38.82</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +711,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>0</v>
@@ -714,53 +721,49 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-0.03)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-0.75)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>712.74</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>655.02</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>631.08</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="G7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>RSI not pulled back (RSI=49.2)</t>
-        </is>
-      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>704.66</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>657.22</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>631.3</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -774,16 +777,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>352.57</v>
+        <v>369.31</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>359.42</v>
+        <v>360.28</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>387.98</v>
+        <v>387.59</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46.84</v>
+        <v>59.67</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -792,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>7.9</v>
+        <v>3.5</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +805,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=46.8)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=59.7)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>343.13</v>
+        <v>340.55</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>326.3</v>
+        <v>326.94</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>292.5</v>
+        <v>292.85</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>72.23999999999999</v>
+        <v>62.63</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -535,17 +535,17 @@
         <v>0</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=72.2); volume elevated on pullback (ratio=1.16)</t>
+          <t>RSI not pulled back (RSI=62.6); volume elevated on pullback (ratio=1.12)</t>
         </is>
       </c>
     </row>
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>534.51</v>
+        <v>533.76</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>506.07</v>
+        <v>506.63</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>434.3</v>
+        <v>434.61</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>65.90000000000001</v>
+        <v>63.79</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -579,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -589,7 +589,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=65.9)</t>
+          <t>RSI not pulled back (RSI=63.8)</t>
         </is>
       </c>
     </row>
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>344.78</v>
+        <v>341.44</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>344.31</v>
+        <v>343.98</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>340.72</v>
+        <v>340.85</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>53.9</v>
+        <v>47.28</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -623,7 +623,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=53.9); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=47.3); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>262.29</v>
+        <v>263.27</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256.83</v>
+        <v>256.54</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>242.89</v>
+        <v>243.07</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>64.04000000000001</v>
+        <v>63.04</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -667,7 +667,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
@@ -677,7 +677,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=64.0)</t>
+          <t>RSI not pulled back (RSI=63.0)</t>
         </is>
       </c>
     </row>
@@ -693,16 +693,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>217.23</v>
+        <v>217.25</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>222.83</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>202.81</v>
+        <v>202.96</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>38.82</v>
+        <v>37.2</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -721,7 +721,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-0.75)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-1.23)</t>
         </is>
       </c>
     </row>
@@ -737,16 +737,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>704.66</v>
+        <v>691.24</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>657.22</v>
+        <v>659.17</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>631.3</v>
+        <v>631.51</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>39.01</v>
+        <v>39.06</v>
       </c>
       <c r="G7" s="2" t="b">
         <v>1</v>
@@ -755,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>9.4</v>
+        <v>11.1</v>
       </c>
       <c r="J7" s="2" t="b">
         <v>1</v>
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>369.31</v>
+        <v>374.75</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>360.28</v>
+        <v>361.13</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>387.59</v>
+        <v>387.27</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>59.67</v>
+        <v>61.25</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -805,7 +805,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=59.7)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=61.2)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -517,26 +517,26 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>340.55</v>
+        <v>344.6</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>326.94</v>
+        <v>327.71</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>292.85</v>
+        <v>293.24</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>62.63</v>
+        <v>71.45</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="1" t="n">
-        <v>0.8</v>
-      </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
       </c>
@@ -545,7 +545,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=62.6); volume elevated on pullback (ratio=1.12)</t>
+          <t>RSI not pulled back (RSI=71.5)</t>
         </is>
       </c>
     </row>
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>533.76</v>
+        <v>532.4299999999999</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>506.63</v>
+        <v>507.18</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>434.61</v>
+        <v>434.92</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>63.79</v>
+        <v>62.66</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -579,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -589,7 +589,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=63.8)</t>
+          <t>RSI not pulled back (RSI=62.7)</t>
         </is>
       </c>
     </row>
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>341.44</v>
+        <v>335.05</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>343.98</v>
+        <v>343.78</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>340.85</v>
+        <v>340.94</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>47.28</v>
+        <v>46.75</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -623,17 +623,17 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>9.5</v>
+        <v>11.2</v>
       </c>
       <c r="J4" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=47.3); SMA50 flattening/falling (trend weakening)</t>
+          <t>price below SMA200; RSI not pulled back (RSI=46.7); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.73)</t>
         </is>
       </c>
     </row>
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>263.27</v>
+        <v>264.29</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256.54</v>
+        <v>256.37</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>243.07</v>
+        <v>243.22</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>63.04</v>
+        <v>64.8</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -667,7 +667,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
@@ -677,7 +677,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=63.0)</t>
+          <t>RSI not pulled back (RSI=64.8)</t>
         </is>
       </c>
     </row>
@@ -693,16 +693,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>217.25</v>
+        <v>221.76</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>222.83</v>
+        <v>222.9</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>202.96</v>
+        <v>203.12</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>37.2</v>
+        <v>40.27</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -711,7 +711,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>0</v>
@@ -721,7 +721,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-1.23)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-1.26)</t>
         </is>
       </c>
     </row>
@@ -737,16 +737,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>691.24</v>
+        <v>708.34</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>659.17</v>
+        <v>661.42</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>631.51</v>
+        <v>631.79</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>39.06</v>
+        <v>44.68</v>
       </c>
       <c r="G7" s="2" t="b">
         <v>1</v>
@@ -755,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>11.1</v>
+        <v>8.9</v>
       </c>
       <c r="J7" s="2" t="b">
         <v>1</v>
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>374.75</v>
+        <v>387.23</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>361.13</v>
+        <v>362.2</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>387.27</v>
+        <v>386.94</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>61.25</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -795,17 +795,17 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=61.2)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=66.5)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -37,12 +37,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,10 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>344.6</v>
+        <v>345.92</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>327.71</v>
+        <v>328.57</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>293.24</v>
+        <v>293.66</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>71.45</v>
+        <v>69.58</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -541,11 +534,11 @@
         <v>1</v>
       </c>
       <c r="K2" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=71.5)</t>
+          <t>RSI not pulled back (RSI=69.6)</t>
         </is>
       </c>
     </row>
@@ -561,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>532.4299999999999</v>
+        <v>524.15</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>507.18</v>
+        <v>507.84</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>434.92</v>
+        <v>435.16</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>62.66</v>
+        <v>54.03</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -579,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -589,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=62.7)</t>
+          <t>RSI not pulled back (RSI=54.0)</t>
         </is>
       </c>
     </row>
@@ -605,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>335.05</v>
+        <v>325.82</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>343.78</v>
+        <v>343.43</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>340.94</v>
+        <v>341</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46.75</v>
+        <v>33.32</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -623,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>11.2</v>
+        <v>13.7</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -633,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>price below SMA200; RSI not pulled back (RSI=46.7); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.73)</t>
+          <t>price below SMA200; SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.16)</t>
         </is>
       </c>
     </row>
@@ -649,25 +642,25 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>264.29</v>
+        <v>250.77</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256.37</v>
+        <v>256</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>243.22</v>
+        <v>243.26</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>64.8</v>
+        <v>49.39</v>
       </c>
       <c r="G5" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>6.9</v>
+        <v>11.7</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
@@ -677,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=64.8)</t>
+          <t>RSI not pulled back (RSI=49.4); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -693,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>221.76</v>
+        <v>212.88</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>222.9</v>
+        <v>222.69</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>203.12</v>
+        <v>203.25</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>40.27</v>
+        <v>30.11</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -711,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>7.3</v>
+        <v>11</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>0</v>
@@ -721,49 +714,53 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-1.26)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-1.93)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>708.34</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>661.42</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>631.79</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>44.68</v>
-      </c>
-      <c r="G7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>647.62</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>662.59</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>631.6799999999999</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>30.11</v>
+      </c>
+      <c r="G7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>volume elevated on pullback (ratio=1.16); pullback too deep (16.7% off high)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -777,25 +774,25 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>387.23</v>
+        <v>378.79</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>362.2</v>
+        <v>363.21</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>386.94</v>
+        <v>386.66</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>66.48999999999999</v>
+        <v>54.51</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H8" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -805,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=66.5)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=54.5); volume elevated on pullback (ratio=1.21)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>345.92</v>
+        <v>346.02</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>328.57</v>
+        <v>329.43</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>293.66</v>
+        <v>294.1</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>69.58</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=69.6)</t>
+          <t>RSI not pulled back (RSI=68.8)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>524.15</v>
+        <v>524.0599999999999</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>507.84</v>
+        <v>508.35</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>435.16</v>
+        <v>435.37</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>54.03</v>
+        <v>49.3</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=54.0)</t>
+          <t>RSI not pulled back (RSI=49.3)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>325.82</v>
+        <v>322.34</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>343.43</v>
+        <v>342.92</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>341</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>33.32</v>
+        <v>27.45</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>price below SMA200; SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.16)</t>
+          <t>price below SMA200; SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-3.61)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>250.77</v>
+        <v>249.02</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>256</v>
+        <v>255.67</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>243.26</v>
+        <v>243.3</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>49.39</v>
+        <v>48.11</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>0</v>
@@ -660,17 +660,17 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=49.4); SMA50 flattening/falling (trend weakening)</t>
+          <t>RSI not pulled back (RSI=48.1); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>212.88</v>
+        <v>211.81</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>222.69</v>
+        <v>222.41</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>203.25</v>
+        <v>203.37</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>30.11</v>
+        <v>22.41</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>0</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-1.93)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-2.56)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>647.62</v>
+        <v>644.72</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>662.59</v>
+        <v>663.62</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>631.6799999999999</v>
+        <v>631.67</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>30.11</v>
+        <v>24.61</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,17 +748,17 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="J7" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>volume elevated on pullback (ratio=1.16); pullback too deep (16.7% off high)</t>
+          <t>volume elevated on pullback (ratio=1.18); pullback too deep (17.1% off high); MACD below zero line (momentum turned negative, MACD=-1.74)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>378.79</v>
+        <v>371.27</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>363.21</v>
+        <v>363.75</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>386.66</v>
+        <v>386.34</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>54.51</v>
+        <v>45.87</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -792,17 +792,17 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=54.5); volume elevated on pullback (ratio=1.21)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=45.9); volume elevated on pullback (ratio=1.10)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>346.02</v>
+        <v>342.97</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>329.43</v>
+        <v>330.21</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>294.1</v>
+        <v>294.53</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>68.79000000000001</v>
+        <v>62.54</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=68.8)</t>
+          <t>RSI not pulled back (RSI=62.5)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>524.0599999999999</v>
+        <v>532.2</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>508.35</v>
+        <v>509.11</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>435.37</v>
+        <v>435.65</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>49.3</v>
+        <v>51.71</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=49.3)</t>
+          <t>RSI not pulled back (RSI=51.7)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>322.34</v>
+        <v>316.96</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>342.92</v>
+        <v>342.3</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>341</v>
+        <v>340.95</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>27.45</v>
+        <v>23.37</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>price below SMA200; SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-3.61)</t>
+          <t>price below SMA200; SMA50 flattening/falling (trend weakening); pullback too deep (16.0% off high); MACD below zero line (momentum turned negative, MACD=-5.16)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>249.02</v>
+        <v>248.26</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>255.67</v>
+        <v>255.36</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>243.3</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>48.11</v>
+        <v>43.21</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>0</v>
@@ -660,17 +660,17 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="J5" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=48.1); SMA50 flattening/falling (trend weakening)</t>
+          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.38)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>211.81</v>
+        <v>216.21</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>222.41</v>
+        <v>222.22</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>203.37</v>
+        <v>203.52</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>22.41</v>
+        <v>29.01</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>0</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-2.56)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-2.69)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>644.72</v>
+        <v>632.61</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>663.62</v>
+        <v>664.4400000000001</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>631.67</v>
+        <v>631.6</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>24.61</v>
+        <v>23.5</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>17.1</v>
+        <v>18.6</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>0</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>volume elevated on pullback (ratio=1.18); pullback too deep (17.1% off high); MACD below zero line (momentum turned negative, MACD=-1.74)</t>
+          <t>volume elevated on pullback (ratio=1.26); pullback too deep (18.6% off high); MACD below zero line (momentum turned negative, MACD=-6.89)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>371.27</v>
+        <v>394.05</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>363.75</v>
+        <v>364.8</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>386.34</v>
+        <v>386.14</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>45.87</v>
+        <v>56.12</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -792,17 +792,17 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=45.9); volume elevated on pullback (ratio=1.10)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=56.1); volume elevated on pullback (ratio=1.15)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>342.97</v>
+        <v>345.54</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>330.21</v>
+        <v>331.03</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>294.53</v>
+        <v>294.97</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>62.54</v>
+        <v>62.71</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,17 +528,17 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=62.5)</t>
+          <t>RSI not pulled back (RSI=62.7)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>532.2</v>
+        <v>530.6799999999999</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>509.11</v>
+        <v>510.14</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>435.65</v>
+        <v>435.93</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>51.71</v>
+        <v>50.53</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=51.7)</t>
+          <t>RSI not pulled back (RSI=50.5)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>316.96</v>
+        <v>321.65</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>342.3</v>
+        <v>341.86</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>340.95</v>
+        <v>340.91</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>23.37</v>
+        <v>25.91</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>16</v>
+        <v>14.8</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>price below SMA200; SMA50 flattening/falling (trend weakening); pullback too deep (16.0% off high); MACD below zero line (momentum turned negative, MACD=-5.16)</t>
+          <t>price below SMA200; SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-5.82)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>248.26</v>
+        <v>253.98</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>255.36</v>
+        <v>255.23</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>243.3</v>
+        <v>243.34</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>43.21</v>
+        <v>45.15</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>0</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>12.6</v>
+        <v>10.6</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.38)</t>
+          <t>RSI not pulled back (RSI=45.2); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.31)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>216.21</v>
+        <v>217.62</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>222.22</v>
+        <v>222.07</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>203.52</v>
+        <v>203.69</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>29.01</v>
+        <v>31.79</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>0</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-2.69)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-2.61)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>632.61</v>
+        <v>622.25</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>664.4400000000001</v>
+        <v>665.47</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>631.6</v>
+        <v>631.4400000000001</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>23.5</v>
+        <v>24.37</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>18.6</v>
+        <v>20</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>0</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>volume elevated on pullback (ratio=1.26); pullback too deep (18.6% off high); MACD below zero line (momentum turned negative, MACD=-6.89)</t>
+          <t>price below SMA200; volume elevated on pullback (ratio=1.48); pullback too deep (20.0% off high); MACD below zero line (momentum turned negative, MACD=-11.67)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>394.05</v>
+        <v>406.07</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>364.8</v>
+        <v>366.09</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>386.14</v>
+        <v>385.93</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>56.12</v>
+        <v>61.94</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=56.1); volume elevated on pullback (ratio=1.15)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=61.9); volume elevated on pullback (ratio=1.20)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>345.54</v>
+        <v>345.2</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>331.03</v>
+        <v>331.76</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>294.97</v>
+        <v>295.41</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>62.71</v>
+        <v>56.92</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=62.7)</t>
+          <t>RSI not pulled back (RSI=56.9)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>530.6799999999999</v>
+        <v>530</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>510.14</v>
+        <v>511.14</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>435.93</v>
+        <v>436.21</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>50.53</v>
+        <v>54.62</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=50.5)</t>
+          <t>RSI not pulled back (RSI=54.6)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>321.65</v>
+        <v>325.32</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>341.86</v>
+        <v>341.46</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>340.91</v>
+        <v>340.88</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>25.91</v>
+        <v>31.27</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>14.8</v>
+        <v>13.8</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>price below SMA200; SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-5.82)</t>
+          <t>price below SMA200; SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-6.04)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>253.98</v>
+        <v>254</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>255.23</v>
+        <v>255.1</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>243.34</v>
+        <v>243.37</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45.15</v>
+        <v>49.95</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=45.2); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.31)</t>
+          <t>RSI not pulled back (RSI=49.9); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.36)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>217.62</v>
+        <v>217.61</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>222.07</v>
+        <v>222.04</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>203.69</v>
+        <v>203.85</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>31.79</v>
+        <v>36.63</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-2.61)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-2.48)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>622.25</v>
+        <v>612.5700000000001</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>665.47</v>
+        <v>666.8200000000001</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>631.4400000000001</v>
+        <v>631.3</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>24.37</v>
+        <v>23.26</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>20</v>
+        <v>21.2</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>0</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>price below SMA200; volume elevated on pullback (ratio=1.48); pullback too deep (20.0% off high); MACD below zero line (momentum turned negative, MACD=-11.67)</t>
+          <t>price below SMA200; volume elevated on pullback (ratio=1.52); pullback too deep (21.2% off high); MACD below zero line (momentum turned negative, MACD=-16.06)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>406.07</v>
+        <v>404.93</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>366.09</v>
+        <v>367.48</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>385.93</v>
+        <v>385.72</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>61.94</v>
+        <v>62.53</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=61.9); volume elevated on pullback (ratio=1.20)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=62.5); volume elevated on pullback (ratio=1.14)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -37,6 +37,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,16 +517,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>345.2</v>
+        <v>350.04</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>331.76</v>
+        <v>332.4</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>295.41</v>
+        <v>295.85</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>56.92</v>
+        <v>67.44</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,63 +535,59 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=56.9)</t>
+          <t>RSI not pulled back (RSI=67.4)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>530</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>511.14</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>436.21</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>54.62</v>
-      </c>
-      <c r="G3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>RSI not pulled back (RSI=54.6)</t>
-        </is>
-      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>526.89</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>512.03</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>436.51</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>44.21</v>
+      </c>
+      <c r="G3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -598,25 +601,25 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>325.32</v>
+        <v>282.4</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>341.46</v>
+        <v>340.21</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>340.88</v>
+        <v>340.61</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>31.27</v>
+        <v>15.38</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H4" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>13.8</v>
+        <v>25.2</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +629,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>price below SMA200; SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-6.04)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.62); pullback too deep (25.2% off high); MACD below zero line (momentum turned negative, MACD=-9.52)</t>
         </is>
       </c>
     </row>
@@ -642,16 +645,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>254</v>
+        <v>244.94</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>255.1</v>
+        <v>254.7</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>243.37</v>
+        <v>243.39</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>49.95</v>
+        <v>34.74</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>0</v>
@@ -660,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>10.6</v>
+        <v>13.8</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +673,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=49.9); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.36)</t>
+          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-1.03)</t>
         </is>
       </c>
     </row>
@@ -686,16 +689,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>217.61</v>
+        <v>212.66</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>222.04</v>
+        <v>221.9</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>203.85</v>
+        <v>203.98</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>36.63</v>
+        <v>33.99</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>9</v>
+        <v>11.1</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>0</v>
@@ -714,7 +717,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-2.48)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-2.91)</t>
         </is>
       </c>
     </row>
@@ -730,16 +733,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>612.5700000000001</v>
+        <v>627.21</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>666.8200000000001</v>
+        <v>668.45</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>631.3</v>
+        <v>631.28</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>23.26</v>
+        <v>28.74</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>21.2</v>
+        <v>19.3</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>0</v>
@@ -758,7 +761,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>price below SMA200; volume elevated on pullback (ratio=1.52); pullback too deep (21.2% off high); MACD below zero line (momentum turned negative, MACD=-16.06)</t>
+          <t>price below SMA200; volume elevated on pullback (ratio=1.39); pullback too deep (19.3% off high); MACD below zero line (momentum turned negative, MACD=-18.02)</t>
         </is>
       </c>
     </row>
@@ -774,22 +777,22 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>404.93</v>
+        <v>405.02</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>367.48</v>
+        <v>368.54</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>385.72</v>
+        <v>385.5</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>62.53</v>
+        <v>59.85</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H8" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>0.6</v>
@@ -802,7 +805,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=62.5); volume elevated on pullback (ratio=1.14)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=59.9)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -37,12 +37,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,10 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>350.04</v>
+        <v>342.93</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>332.4</v>
+        <v>333.01</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>295.85</v>
+        <v>296.26</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>67.44</v>
+        <v>52.52</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -535,59 +528,63 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=67.4)</t>
+          <t>RSI not pulled back (RSI=52.5)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>526.89</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>512.03</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>436.51</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>44.21</v>
-      </c>
-      <c r="G3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>520.47</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>512.88</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>436.85</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="G3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>volume elevated on pullback (ratio=1.17)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -601,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>282.4</v>
+        <v>277.83</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>340.21</v>
+        <v>338.99</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>340.61</v>
+        <v>340.33</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>15.38</v>
+        <v>13.83</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -619,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>25.2</v>
+        <v>26.4</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -629,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.62); pullback too deep (25.2% off high); MACD below zero line (momentum turned negative, MACD=-9.52)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.87); pullback too deep (26.4% off high); MACD below zero line (momentum turned negative, MACD=-12.39)</t>
         </is>
       </c>
     </row>
@@ -645,25 +642,25 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>244.94</v>
+        <v>238.07</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>254.7</v>
+        <v>254.23</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>243.39</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>34.74</v>
+        <v>32.49</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H5" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -673,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-1.03)</t>
+          <t>price below SMA200; SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.29); MACD below zero line (momentum turned negative, MACD=-2.20)</t>
         </is>
       </c>
     </row>
@@ -689,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>212.66</v>
+        <v>201.98</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>221.9</v>
+        <v>221.63</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>203.98</v>
+        <v>204.08</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>33.99</v>
+        <v>29.59</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -707,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>0</v>
@@ -717,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-2.91)</t>
+          <t>price below SMA200; pullback too deep (15.6% off high); MACD below zero line (momentum turned negative, MACD=-3.86)</t>
         </is>
       </c>
     </row>
@@ -733,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>627.21</v>
+        <v>615.11</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>668.45</v>
+        <v>669.79</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>631.28</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>28.74</v>
+        <v>17.64</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -751,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>19.3</v>
+        <v>20.9</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>0</v>
@@ -761,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>price below SMA200; volume elevated on pullback (ratio=1.39); pullback too deep (19.3% off high); MACD below zero line (momentum turned negative, MACD=-18.02)</t>
+          <t>price below SMA200; volume elevated on pullback (ratio=1.45); pullback too deep (20.9% off high); MACD below zero line (momentum turned negative, MACD=-20.47)</t>
         </is>
       </c>
     </row>
@@ -777,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>405.02</v>
+        <v>395.1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>368.54</v>
+        <v>369.51</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>385.5</v>
+        <v>385.28</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>59.85</v>
+        <v>57.3</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -795,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -805,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=59.9)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=57.3)</t>
         </is>
       </c>
     </row>
